--- a/outputs/forecast_housing_pressure_by_tract.xlsx
+++ b/outputs/forecast_housing_pressure_by_tract.xlsx
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>4.049495752297845</v>
+        <v>3.959337547206555</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>3.918412500597036</v>
+        <v>3.798984598309185</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>3.833888769252702</v>
+        <v>3.743344162242367</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>28.20742765501014</v>
+        <v>31.71883272440452</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>31.54068275015168</v>
+        <v>34.28225151558129</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>34.22611708431914</v>
+        <v>36.6772670129716</v>
       </c>
     </row>
     <row r="12">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>36.77805015247488</v>
+        <v>40.08714208214852</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>40.19253563218121</v>
+        <v>43.80889880843557</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>43.92407683421112</v>
+        <v>47.87618961204926</v>
       </c>
     </row>
     <row r="17">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>30.35094137853919</v>
+        <v>29.67615639703399</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>29.69858054451321</v>
+        <v>29.01055529913296</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>29.01106081789249</v>
+        <v>28.34647075751052</v>
       </c>
     </row>
     <row r="22">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>6.703383070104246</v>
+        <v>6.878200529000753</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>6.87973154526762</v>
+        <v>7.058905595650588</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>7.060487490348359</v>
+        <v>7.244356346393737</v>
       </c>
     </row>
     <row r="27">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>17.46547425408255</v>
+        <v>17.29377730431385</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>17.29360422391309</v>
+        <v>17.13075371840273</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>17.13131984335682</v>
+        <v>16.96942850735389</v>
       </c>
     </row>
     <row r="32">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>19.92863701184596</v>
+        <v>19.40510401128897</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>19.41182140483668</v>
+        <v>18.92240136021056</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>18.92680184257647</v>
+        <v>18.45290015622987</v>
       </c>
     </row>
     <row r="37">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>1.164740970863652</v>
+        <v>0.97041575788928</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>0.9800794703143656</v>
+        <v>0.8165564571170133</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>0.824687914381205</v>
+        <v>0.6870915281373218</v>
       </c>
     </row>
     <row r="42">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>17.5400618509355</v>
+        <v>17.00916323195869</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>17.01210592758499</v>
+        <v>16.47046027238103</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>16.4757905186897</v>
+        <v>15.94774805172939</v>
       </c>
     </row>
     <row r="47">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>30.19055201691076</v>
+        <v>30.17563815458499</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>30.18479120667913</v>
+        <v>30.21092314657925</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>30.21462697816699</v>
+        <v>30.25731963333674</v>
       </c>
     </row>
     <row r="52">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>22.08997894003186</v>
+        <v>21.87274219880285</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>21.72999656052686</v>
+        <v>21.53186271803897</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>21.60050835616732</v>
+        <v>21.39692015166015</v>
       </c>
     </row>
     <row r="57">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>27.8243076620154</v>
+        <v>27.79387243613509</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>27.78337582318798</v>
+        <v>27.68875427051756</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>27.68630387884116</v>
+        <v>27.57628492987082</v>
       </c>
     </row>
     <row r="62">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>23.68871789459865</v>
+        <v>23.25500958038098</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>23.20696736222141</v>
+        <v>22.57482706977678</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>22.55521120818561</v>
+        <v>21.83579697439906</v>
       </c>
     </row>
     <row r="67">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>5.349728811440059</v>
+        <v>4.511294347620559</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>4.754900901072184</v>
+        <v>4.105399666896782</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>4.006885469567788</v>
+        <v>3.403962394186022</v>
       </c>
     </row>
     <row r="72">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>18.50230368161611</v>
+        <v>17.15785867290092</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>17.1890310299814</v>
+        <v>15.94779525732165</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>15.97627738720912</v>
+        <v>14.82317823140478</v>
       </c>
     </row>
     <row r="77">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>17.53144327136995</v>
+        <v>18.16846893576726</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>18.05516013878885</v>
+        <v>18.67449049049509</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>18.75440236400262</v>
+        <v>19.42024766574552</v>
       </c>
     </row>
     <row r="82">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>0.4403620764277723</v>
+        <v>0.3173720305521067</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>0.3282794080344679</v>
+        <v>0.2533722069150921</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>0.2589713931412509</v>
+        <v>0.2061699419565539</v>
       </c>
     </row>
     <row r="87">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>36.19349241898745</v>
+        <v>36.36917020318152</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>35.77193353894444</v>
+        <v>35.92597294886396</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>36.23428243136622</v>
+        <v>36.40770414205318</v>
       </c>
     </row>
     <row r="92">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>9.92684054604093</v>
+        <v>8.910052584245038</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>8.97710656781244</v>
+        <v>8.218704587972859</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>8.257711558259333</v>
+        <v>7.644377502560101</v>
       </c>
     </row>
     <row r="97">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>22.84679433335407</v>
+        <v>23.19170465547668</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>23.19045527176915</v>
+        <v>23.55903514269329</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>23.56140062394017</v>
+        <v>23.93346207365055</v>
       </c>
     </row>
     <row r="102">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>1.969478672118353</v>
+        <v>1.828010243478197</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>1.773349178163413</v>
+        <v>1.64102932185916</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>1.673851162979826</v>
+        <v>1.552513923602121</v>
       </c>
     </row>
     <row r="107">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>46.14401064424491</v>
+        <v>45.48409549446422</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>45.46762871795096</v>
+        <v>44.85151823967216</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>44.85940694879815</v>
+        <v>44.24260711225808</v>
       </c>
     </row>
     <row r="112">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>0.5421690897683816</v>
+        <v>0.4073317235630454</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>0.4167791149648958</v>
+        <v>0.3131262155064159</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>0.3203886646232998</v>
+        <v>0.2407080548004381</v>
       </c>
     </row>
     <row r="117">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>26.98026684012669</v>
+        <v>29.78683048471213</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>29.85164294414345</v>
+        <v>32.80894238100153</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>32.8973658244298</v>
+        <v>36.09632460757574</v>
       </c>
     </row>
     <row r="122">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>38.6074334532822</v>
+        <v>39.12110211248902</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>38.32156535100042</v>
+        <v>38.37591872155708</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>38.94058771157648</v>
+        <v>39.32474230068334</v>
       </c>
     </row>
     <row r="127">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>25.33105184540887</v>
+        <v>24.0851896037955</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>24.06892478981086</v>
+        <v>22.86684546518638</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>22.90996265280478</v>
+        <v>21.77785288943248</v>
       </c>
     </row>
     <row r="132">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>18.96451788636095</v>
+        <v>16.57236191848978</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>16.53302021032529</v>
+        <v>14.45302256039795</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>14.5936980226954</v>
+        <v>12.75570958919846</v>
       </c>
     </row>
     <row r="137">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>40.23425260872735</v>
+        <v>40.24248596983931</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>40.24248689556435</v>
+        <v>40.25066560863775</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>40.25066616041038</v>
+        <v>40.25884690275408</v>
       </c>
     </row>
     <row r="142">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>7.105699927650517</v>
+        <v>7.056953792284573</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>7.083717590589532</v>
+        <v>7.009728076992711</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>7.001081798866778</v>
+        <v>6.936563527323052</v>
       </c>
     </row>
     <row r="147">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>48.07870669974136</v>
+        <v>50.49586344635684</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>50.53750871126467</v>
+        <v>53.08665329014527</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>53.1309942208019</v>
+        <v>55.81046592590361</v>
       </c>
     </row>
     <row r="152">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>11.87688667885827</v>
+        <v>11.71531836205499</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>11.42910295360385</v>
+        <v>11.05190630511656</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>11.28911426422976</v>
+        <v>11.10011812551774</v>
       </c>
     </row>
     <row r="157">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>4.020676806117253</v>
+        <v>3.77132404346727</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>3.7762705523717</v>
+        <v>3.542060704135714</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>3.5467064354977</v>
+        <v>3.326734558890118</v>
       </c>
     </row>
     <row r="162">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>24.89189929439211</v>
+        <v>26.15852876084345</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>26.1807484646593</v>
+        <v>27.51179476950369</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>27.53513008739246</v>
+        <v>28.93506673183024</v>
       </c>
     </row>
     <row r="167">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>25.47069851718213</v>
+        <v>25.48623719388854</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>25.48963854628232</v>
+        <v>25.48414072571278</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>25.48372584753127</v>
+        <v>25.48079962299249</v>
       </c>
     </row>
     <row r="172">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>33.76758705331167</v>
+        <v>35.38093307293403</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>35.40751712124466</v>
+        <v>37.10022494349839</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>37.12807471916751</v>
+        <v>38.90306614107011</v>
       </c>
     </row>
     <row r="177">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>8.261403236689729</v>
+        <v>7.75206128576329</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>7.773647719662113</v>
+        <v>7.27832928113027</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>7.285280337850733</v>
+        <v>6.825450446658643</v>
       </c>
     </row>
     <row r="182">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>17.39023104917741</v>
+        <v>17.72619094055606</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>17.67876141925413</v>
+        <v>17.82035161178238</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>17.79817614985874</v>
+        <v>17.84798589723779</v>
       </c>
     </row>
     <row r="187">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>1.33297555883785</v>
+        <v>1.394894147398686</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>1.396118008002677</v>
+        <v>1.458735362612856</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>1.459673607344633</v>
+        <v>1.525391312022357</v>
       </c>
     </row>
     <row r="192">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>18.79563140179863</v>
+        <v>19.01142293102165</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>18.93310082356239</v>
+        <v>19.21243348936309</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>19.24276482223704</v>
+        <v>19.50443804632637</v>
       </c>
     </row>
     <row r="197">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>36.19500971483401</v>
+        <v>35.72775105403999</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>35.74262534980522</v>
+        <v>35.34505931888817</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>35.35109876138353</v>
+        <v>34.98048591122242</v>
       </c>
     </row>
     <row r="202">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>37.48780593847528</v>
+        <v>37.59041844501279</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>37.59038386295966</v>
+        <v>37.69606118557973</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>37.69616603633924</v>
+        <v>37.80201847842517</v>
       </c>
     </row>
     <row r="207">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>9.527959261448849</v>
+        <v>9.763422487999094</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>9.754202859823502</v>
+        <v>10.02255777892462</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>10.0277123592017</v>
+        <v>10.2971568106814</v>
       </c>
     </row>
     <row r="212">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>9.103552984310872</v>
+        <v>8.696019574796747</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>8.701622790652296</v>
+        <v>8.31465274120241</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>8.320242162277507</v>
+        <v>7.950054170833365</v>
       </c>
     </row>
     <row r="217">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>7.246259063037989</v>
+        <v>6.940680943723099</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>6.843452641346498</v>
+        <v>6.583484681521293</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>6.630549717351356</v>
+        <v>6.367483526809673</v>
       </c>
     </row>
     <row r="222">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>8.66914378232943</v>
+        <v>9.553887944139662</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>9.587650391519068</v>
+        <v>10.57530976500443</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>10.61187190836875</v>
+        <v>11.70641801596216</v>
       </c>
     </row>
     <row r="227">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>8.838965260697517</v>
+        <v>8.354122318397216</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>8.357487374639723</v>
+        <v>7.921211640512452</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>7.929232115603614</v>
+        <v>7.51236238790117</v>
       </c>
     </row>
     <row r="232">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>14.61523270759525</v>
+        <v>15.14808228261691</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>15.15235636007736</v>
+        <v>15.71318881209953</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>15.72074521774924</v>
+        <v>16.30096455853129</v>
       </c>
     </row>
     <row r="237">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>24.9848697232369</v>
+        <v>24.59715843917245</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>24.60602345114363</v>
+        <v>24.20402923891289</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>24.20484794495321</v>
+        <v>23.81335615677431</v>
       </c>
     </row>
     <row r="242">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>27.43665356629834</v>
+        <v>29.86955072615473</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>29.92190700724699</v>
+        <v>32.6333776305154</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>32.72667370187936</v>
+        <v>35.67709274896793</v>
       </c>
     </row>
     <row r="247">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>10.10793973812801</v>
+        <v>10.47842615150089</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>10.48304036245644</v>
+        <v>10.86687970919583</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>10.87167926858533</v>
+        <v>11.26973194505927</v>
       </c>
     </row>
     <row r="252">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>14.69547240249143</v>
+        <v>15.1484512488764</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>15.15294596885053</v>
+        <v>15.62125742403166</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>15.6262238512568</v>
+        <v>16.10896288086234</v>
       </c>
     </row>
     <row r="257">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>17.27285432978145</v>
+        <v>18.59982291475216</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>17.5715151699943</v>
+        <v>17.37005421314113</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>17.21223687157297</v>
+        <v>15.6668334868256</v>
       </c>
     </row>
     <row r="262">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>2.853436789528013</v>
+        <v>2.32382873322308</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>2.352666388672739</v>
+        <v>1.920218740131997</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>1.943628125614102</v>
+        <v>1.586836903487227</v>
       </c>
     </row>
     <row r="267">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>6.102829495217868</v>
+        <v>5.526678705375866</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>5.541811978971301</v>
+        <v>5.022658076138863</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>5.038268950926258</v>
+        <v>4.565470071264046</v>
       </c>
     </row>
     <row r="272">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>2.103930508707387</v>
+        <v>1.825460828830698</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>1.839720543867938</v>
+        <v>1.61606119331162</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>1.625547226600314</v>
+        <v>1.435119657658623</v>
       </c>
     </row>
     <row r="277">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>25.89690483834631</v>
+        <v>26.75078618064467</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>26.78291038464843</v>
+        <v>27.6208339539374</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>27.6238582080536</v>
+        <v>28.49995448957873</v>
       </c>
     </row>
     <row r="282">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>41.14433637505526</v>
+        <v>41.32360450700787</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>41.32642754855872</v>
+        <v>41.52054180192688</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>41.52156954339171</v>
+        <v>41.72056232124037</v>
       </c>
     </row>
     <row r="287">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>15.7805214225695</v>
+        <v>14.05744437839495</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>14.11574482634227</v>
+        <v>12.57444496555462</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>12.62659496766345</v>
+        <v>11.24789555904078</v>
       </c>
     </row>
     <row r="292">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>39.97228261891306</v>
+        <v>38.65502332123602</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>41.82374410265538</v>
+        <v>43.54972484190975</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>40.50413187004431</v>
+        <v>39.30764744698717</v>
       </c>
     </row>
     <row r="297">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>22.32321074895907</v>
+        <v>23.04375086975618</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>21.92607031481531</v>
+        <v>21.57328761004459</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>22.65023076657585</v>
+        <v>23.33365381992676</v>
       </c>
     </row>
     <row r="302">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>3.280037047620534</v>
+        <v>2.667621671046183</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>2.713302501213667</v>
+        <v>2.203238603967232</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>2.226799705485</v>
+        <v>1.809538841441585</v>
       </c>
     </row>
     <row r="307">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>15.34464515548519</v>
+        <v>15.5939614614347</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>15.59401928252298</v>
+        <v>15.8615864106506</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>15.86324810592429</v>
+        <v>16.13419644568756</v>
       </c>
     </row>
     <row r="312">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>22.54492566590724</v>
+        <v>22.48912806421695</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>22.48951247276351</v>
+        <v>22.43134432747595</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>22.43135887660261</v>
+        <v>22.37360423811492</v>
       </c>
     </row>
     <row r="317">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>38.45646906661556</v>
+        <v>38.10805836140415</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>38.27585944963194</v>
+        <v>37.98737674136241</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>37.88756656408727</v>
+        <v>37.56726458949525</v>
       </c>
     </row>
     <row r="322">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>3.924493075324537</v>
+        <v>5.397777267561644</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>5.636079895776457</v>
+        <v>7.751966433978644</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>8.094224221236807</v>
+        <v>11.13292896217013</v>
       </c>
     </row>
     <row r="327">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>2.089797443448752</v>
+        <v>2.329881990222025</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>2.339133675604146</v>
+        <v>2.611951426923321</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>2.62354049500165</v>
+        <v>2.928788067859604</v>
       </c>
     </row>
     <row r="332">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>21.73077487176632</v>
+        <v>21.5415919071413</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>21.38464476071802</v>
+        <v>21.11858891967478</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>21.22506214448917</v>
+        <v>21.01500560665143</v>
       </c>
     </row>
     <row r="337">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>2.483143801369295</v>
+        <v>2.740178943119087</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>2.749468455470832</v>
+        <v>3.033006648150475</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>3.04340171644801</v>
+        <v>3.357019558074466</v>
       </c>
     </row>
     <row r="342">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>0.531946266374428</v>
+        <v>0.4241379898298857</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>0.4304498531721179</v>
+        <v>0.3438707150370615</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>0.3489375300778228</v>
+        <v>0.2788038853665213</v>
       </c>
     </row>
     <row r="347">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>1.30078196548735</v>
+        <v>1.223044704938809</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>1.230594674293731</v>
+        <v>1.181634451854454</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>1.185946598368153</v>
+        <v>1.153160638311196</v>
       </c>
     </row>
     <row r="352">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>8.355030153164561</v>
+        <v>8.060371845490547</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>8.06361855206133</v>
+        <v>7.777747313164913</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>7.781027191463481</v>
+        <v>7.50496241573498</v>
       </c>
     </row>
     <row r="357">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>26.54299635848736</v>
+        <v>31.25963436482634</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>31.57478336687759</v>
+        <v>37.18701152905537</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>37.56176515627399</v>
+        <v>44.23864957494025</v>
       </c>
     </row>
     <row r="362">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>9.984436088852833</v>
+        <v>9.785601370532547</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>9.836547926014161</v>
+        <v>9.54315413956442</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>9.534073736939844</v>
+        <v>9.273465700722561</v>
       </c>
     </row>
     <row r="367">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>24.2266858144359</v>
+        <v>22.31179670507515</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>22.27393150948798</v>
+        <v>20.64094455821495</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>20.70115227927473</v>
+        <v>19.1507155745341</v>
       </c>
     </row>
     <row r="372">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>3.990204133734051</v>
+        <v>3.311997682685101</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>3.362318050426244</v>
+        <v>2.765356969564413</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>2.793370757114111</v>
+        <v>2.302757619092819</v>
       </c>
     </row>
     <row r="377">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>2.053443423196967</v>
+        <v>1.674126871921311</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>1.694757205954202</v>
+        <v>1.381697955648063</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>1.398724676164692</v>
+        <v>1.140349200924701</v>
       </c>
     </row>
     <row r="382">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>11.41885095803803</v>
+        <v>11.09623386725406</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>10.89739822968149</v>
+        <v>10.57445378207258</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>10.682148913999</v>
+        <v>10.37575909267038</v>
       </c>
     </row>
     <row r="387">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>10.3323421758016</v>
+        <v>9.420836967495264</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>9.447445904510408</v>
+        <v>8.609491879874509</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>8.632648203000841</v>
+        <v>7.86761576163275</v>
       </c>
     </row>
     <row r="392">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>41.78845754156011</v>
+        <v>43.95195208277597</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>43.91929009697304</v>
+        <v>46.30351645706918</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>46.36980043819046</v>
+        <v>48.85393277472624</v>
       </c>
     </row>
     <row r="397">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>32.77873429034136</v>
+        <v>31.94384224032969</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>31.95081126102221</v>
+        <v>31.13700685732041</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>31.14379985496483</v>
+        <v>30.35055046724437</v>
       </c>
     </row>
     <row r="407">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>4.642678310953213</v>
+        <v>3.389339670795071</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>3.475427489527996</v>
+        <v>2.553261090750315</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>2.622379629898709</v>
+        <v>1.92453812815074</v>
       </c>
     </row>
     <row r="412">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>29.40132591204983</v>
+        <v>27.95933284354394</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>27.98179215167107</v>
+        <v>26.60162992954105</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>26.62355596442353</v>
+        <v>25.3097051201856</v>
       </c>
     </row>
     <row r="417">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>23.98500353152434</v>
+        <v>22.59565725448778</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>23.05560747979318</v>
+        <v>22.03262025929254</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>21.71441089013909</v>
+        <v>20.51495515663695</v>
       </c>
     </row>
     <row r="422">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>43.88058766814142</v>
+        <v>42.60765847048668</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>46.96427653659896</v>
+        <v>48.87220861457705</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>45.47934345351005</v>
+        <v>44.95816327546643</v>
       </c>
     </row>
     <row r="427">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>33.63802805061638</v>
+        <v>33.02928719458548</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>32.96582855372309</v>
+        <v>32.41733081542691</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>32.4447304009271</v>
+        <v>31.8875731927689</v>
       </c>
     </row>
     <row r="432">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>31.43776174599664</v>
+        <v>30.71862771344194</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>30.7248250434082</v>
+        <v>30.0313935833338</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>30.03662888989069</v>
+        <v>29.35986537289633</v>
       </c>
     </row>
     <row r="437">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>40.8418960643603</v>
+        <v>41.41205195628596</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>41.45390530182527</v>
+        <v>42.16870871679783</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>42.19848573996151</v>
+        <v>43.01469654680074</v>
       </c>
     </row>
     <row r="442">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>5.805497225990887</v>
+        <v>5.649088724111634</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>5.650444904183755</v>
+        <v>5.496922104532606</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>5.498286667214636</v>
+        <v>5.34884917299967</v>
       </c>
     </row>
     <row r="447">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>45.30420225158101</v>
+        <v>44.5880050973147</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>44.59166925078866</v>
+        <v>43.88740678095818</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>43.89108102576265</v>
+        <v>43.19783119901509</v>
       </c>
     </row>
     <row r="452">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>33.10582604621829</v>
+        <v>31.41139380177491</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>31.43926298479635</v>
+        <v>29.82466664633598</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>29.85137225726969</v>
+        <v>28.31805632369819</v>
       </c>
     </row>
     <row r="457">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>21.79368948227003</v>
+        <v>23.18465673376436</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>22.35921517727341</v>
+        <v>22.96941245348548</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>23.81114760989327</v>
+        <v>25.27937364242997</v>
       </c>
     </row>
     <row r="462">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>54.9122779368067</v>
+        <v>56.87094064336497</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>56.95893563939998</v>
+        <v>59.04355886154612</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>59.01440109223488</v>
+        <v>61.12870377179357</v>
       </c>
     </row>
     <row r="467">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>14.96488796691847</v>
+        <v>16.54860077473158</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>16.60856728012201</v>
+        <v>18.36629540435779</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>18.43284717153031</v>
+        <v>20.38364533550156</v>
       </c>
     </row>
     <row r="472">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>30.71944745527907</v>
+        <v>31.06274020380032</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>31.06721936730802</v>
+        <v>31.39540166958601</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>31.39614637376141</v>
+        <v>31.7302972478979</v>
       </c>
     </row>
     <row r="477">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>25.48835982901538</v>
+        <v>25.55110230855952</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>25.54979782058416</v>
+        <v>25.61873632715332</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>25.61901012721704</v>
+        <v>25.68719174593827</v>
       </c>
     </row>
     <row r="482">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>6.343752780186666</v>
+        <v>6.471028280753269</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>6.439292877309062</v>
+        <v>6.593976433394303</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>6.607268123641544</v>
+        <v>6.756799656777059</v>
       </c>
     </row>
     <row r="487">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>25.00505748140058</v>
+        <v>22.89334137349005</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>23.60721945616419</v>
+        <v>22.03674957812072</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>21.59888083501872</v>
+        <v>19.86655155344539</v>
       </c>
     </row>
     <row r="492">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>15.53695582833053</v>
+        <v>15.70497042931084</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>15.75142306076743</v>
+        <v>15.94172500871091</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>15.91311109494012</v>
+        <v>16.09263784679862</v>
       </c>
     </row>
     <row r="497">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>18.55016482581677</v>
+        <v>17.1483110030547</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>16.88121638813845</v>
+        <v>15.68513821710776</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>15.84041219571115</v>
+        <v>14.68778736697098</v>
       </c>
     </row>
     <row r="502">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>46.4897796795378</v>
+        <v>47.42832737406223</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>47.44039271389733</v>
+        <v>48.39943573829602</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>48.40275929026371</v>
+        <v>49.38051475843288</v>
       </c>
     </row>
     <row r="507">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>37.42674487058351</v>
+        <v>36.42304044129548</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>36.44243004885325</v>
+        <v>35.41199583439765</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>35.42016641930799</v>
+        <v>34.42546298223083</v>
       </c>
     </row>
     <row r="512">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>27.92451658493807</v>
+        <v>27.04643392633087</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>27.31946839182684</v>
+        <v>26.37391386241353</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>26.27458639452439</v>
+        <v>25.40341139482878</v>
       </c>
     </row>
     <row r="517">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>26.11703326042185</v>
+        <v>24.58995783142865</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>27.62039226819271</v>
+        <v>28.87153690824702</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>25.88840671333979</v>
+        <v>24.20372540034372</v>
       </c>
     </row>
     <row r="522">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>43.84117541442534</v>
+        <v>44.373170875629</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>44.18650483511399</v>
+        <v>44.8327726526539</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>44.91022445143074</v>
+        <v>45.52472982600931</v>
       </c>
     </row>
     <row r="527">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>19.83603209317778</v>
+        <v>18.78161227849739</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>18.95301727790677</v>
+        <v>17.88747001916798</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>17.84507876423118</v>
+        <v>16.86615399502815</v>
       </c>
     </row>
     <row r="532">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>30.18181753304133</v>
+        <v>30.6079612106095</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>30.60998588751691</v>
+        <v>31.04219142902031</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>31.04424488058211</v>
+        <v>31.48258200211652</v>
       </c>
     </row>
     <row r="537">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>5.427410433592322</v>
+        <v>4.914169750570387</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>4.929358400571012</v>
+        <v>4.463205382557279</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>4.477000106941606</v>
+        <v>4.053625187697152</v>
       </c>
     </row>
     <row r="542">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>3.346633152371091</v>
+        <v>3.51089304618679</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>3.491211587111115</v>
+        <v>3.673934828029061</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>3.686610267546793</v>
+        <v>3.875002928424528</v>
       </c>
     </row>
     <row r="547">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>17.62885872163715</v>
+        <v>16.19077861767156</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>16.26216607464298</v>
+        <v>14.96252575550219</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>14.96774502480942</v>
+        <v>13.7499307012545</v>
       </c>
     </row>
     <row r="552">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>59.33310390322809</v>
+        <v>70.35854830156222</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>71.13216820829061</v>
+        <v>84.35014795181775</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>85.27761099882839</v>
+        <v>100</v>
       </c>
     </row>
     <row r="557">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>33.3087232698016</v>
+        <v>35.92083402049681</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>37.65422865449037</v>
+        <v>42.36642939309045</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>40.75940508486579</v>
+        <v>43.99095184101011</v>
       </c>
     </row>
     <row r="562">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>3.386044836435104</v>
+        <v>2.989303926147591</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>3.04661316257546</v>
+        <v>2.893552427350201</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>2.922093698754607</v>
+        <v>2.883424742766029</v>
       </c>
     </row>
     <row r="567">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>23.05780806833316</v>
+        <v>22.48205928944366</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>22.48675391974466</v>
+        <v>21.92500294289003</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>21.9296015875171</v>
+        <v>21.38174253021763</v>
       </c>
     </row>
     <row r="572">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>32.92835159887474</v>
+        <v>33.34463073457343</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>33.34879502853723</v>
+        <v>33.74850028457632</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>33.74987845877004</v>
+        <v>34.15650435716038</v>
       </c>
     </row>
     <row r="577">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>33.78376038839736</v>
+        <v>34.34730622290171</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>34.27809192716003</v>
+        <v>34.95667814464462</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>34.98260632014088</v>
+        <v>35.6438345928763</v>
       </c>
     </row>
     <row r="582">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>51.84278180843703</v>
+        <v>54.13531061760087</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>54.17395582986381</v>
+        <v>56.56892895693809</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>56.60346125192575</v>
+        <v>59.10614418123828</v>
       </c>
     </row>
     <row r="587">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>10.45738475482635</v>
+        <v>7.641468934194878</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>7.835284393589515</v>
+        <v>5.723108904603497</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>5.889075773980977</v>
+        <v>4.302649483144553</v>
       </c>
     </row>
     <row r="592">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>14.64500529407526</v>
+        <v>12.90319380605201</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>12.88312114983114</v>
+        <v>11.44247577781764</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>11.51612203075226</v>
+        <v>10.20269650838711</v>
       </c>
     </row>
     <row r="597">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>17.29391663954699</v>
+        <v>19.39267495369372</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>19.44698778755322</v>
+        <v>21.64137432047172</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>21.72051019582256</v>
+        <v>24.12748131330222</v>
       </c>
     </row>
     <row r="602">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>30.13061145096522</v>
+        <v>28.81849485543382</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>28.69357095622736</v>
+        <v>27.40371103464414</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>27.50463215125759</v>
+        <v>26.29169056369478</v>
       </c>
     </row>
     <row r="607">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>26.57978397499672</v>
+        <v>25.66711201751924</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>25.6714670609618</v>
+        <v>24.8153942372114</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>24.82552735008494</v>
+        <v>23.99407579552416</v>
       </c>
     </row>
     <row r="612">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>6.038265793087472</v>
+        <v>5.717128806952922</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>5.718920830227741</v>
+        <v>5.384604248380986</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>5.390092049586645</v>
+        <v>5.068543093426026</v>
       </c>
     </row>
     <row r="617">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>15.89622978766308</v>
+        <v>16.62053251869868</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>16.63262137277798</v>
+        <v>17.39385044604941</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>17.40607750976677</v>
+        <v>18.20384956455223</v>
       </c>
     </row>
     <row r="622">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>28.75967892238837</v>
+        <v>30.57043884114083</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>30.48023250249466</v>
+        <v>31.87358759034943</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>31.84542148238954</v>
+        <v>33.09223801567835</v>
       </c>
     </row>
     <row r="627">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>23.65492568137431</v>
+        <v>23.82776062896729</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>23.75026321688744</v>
+        <v>23.53574016960786</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>23.51160230027574</v>
+        <v>23.17130610225208</v>
       </c>
     </row>
     <row r="632">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>11.54873520989667</v>
+        <v>10.44841099488136</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>10.47625820782043</v>
+        <v>9.488017814487176</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>9.51823668327269</v>
+        <v>8.61828124044953</v>
       </c>
     </row>
     <row r="637">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>22.47761968878724</v>
+        <v>22.50417655979727</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>22.50522478066883</v>
+        <v>22.52945619729789</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>22.52922153695271</v>
+        <v>22.55403185376297</v>
       </c>
     </row>
     <row r="642">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>14.29061792442735</v>
+        <v>13.30562642394848</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>13.32625473416322</v>
+        <v>12.41385075197366</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>12.43382745030879</v>
+        <v>11.58200517500424</v>
       </c>
     </row>
     <row r="647">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>5.607133170894866</v>
+        <v>4.704449443667779</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>4.747898404787661</v>
+        <v>3.983989489595364</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>4.020768103402681</v>
+        <v>3.373865376944901</v>
       </c>
     </row>
     <row r="652">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>45.73624154333572</v>
+        <v>44.99359583030453</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>44.99720503853422</v>
+        <v>44.26919184027038</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>44.27311274292333</v>
+        <v>43.55655055819508</v>
       </c>
     </row>
     <row r="657">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>19.88222989156682</v>
+        <v>18.69157386938266</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>18.71441487172822</v>
+        <v>17.5935118636983</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>17.61501419544824</v>
+        <v>16.55995685326377</v>
       </c>
     </row>
     <row r="662">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>15.98176627637522</v>
+        <v>15.30061926149637</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>15.31423969329034</v>
+        <v>14.65321255729861</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>14.6614665643806</v>
+        <v>14.03056787434682</v>
       </c>
     </row>
     <row r="667">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>34.69205012606023</v>
+        <v>35.59794843238726</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>35.6059614870714</v>
+        <v>36.53557480051267</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>36.54380644218775</v>
+        <v>37.49789609366333</v>
       </c>
     </row>
     <row r="672">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>33.72628789837557</v>
+        <v>32.56864700041353</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>32.6943426858258</v>
+        <v>32.01664828514962</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>32.08737894596896</v>
+        <v>31.67684155234373</v>
       </c>
     </row>
     <row r="677">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>50.60204628646881</v>
+        <v>54.36009137881533</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>54.20628739625946</v>
+        <v>57.41521857245269</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>57.32427257196923</v>
+        <v>60.19750776463967</v>
       </c>
     </row>
     <row r="682">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>23.78041799951931</v>
+        <v>23.36458399614279</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>23.34331004771283</v>
+        <v>22.95573909161221</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>22.96598410028053</v>
+        <v>22.5776292130866</v>
       </c>
     </row>
     <row r="687">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>14.50267973558974</v>
+        <v>12.9633181742933</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>13.014304987769</v>
+        <v>11.63177636549469</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>11.67735258179511</v>
+        <v>10.43696320559733</v>
       </c>
     </row>
     <row r="692">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>17.45205674661153</v>
+        <v>15.67338436326867</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>15.75308411696898</v>
+        <v>14.32053581656133</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>14.36826570515971</v>
+        <v>13.11087693564913</v>
       </c>
     </row>
     <row r="697">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>33.92590881399834</v>
+        <v>33.69974838954436</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>33.58195648818059</v>
+        <v>33.33339547738156</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>33.39997832648092</v>
+        <v>33.16679111251684</v>
       </c>
     </row>
     <row r="702">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>9.930166074838576</v>
+        <v>9.017293912011827</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>9.036539919724719</v>
+        <v>8.163375348773274</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>8.18727547561749</v>
+        <v>7.381157166067368</v>
       </c>
     </row>
     <row r="707">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>11.95975967913331</v>
+        <v>10.80358974237571</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>10.83678477356178</v>
+        <v>9.769803535183673</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>9.80226018551217</v>
+        <v>8.833387278977121</v>
       </c>
     </row>
     <row r="712">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>26.28497299006274</v>
+        <v>26.36624979674367</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>26.36727639006315</v>
+        <v>26.44612604116309</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>26.44600899624889</v>
+        <v>26.52565115083988</v>
       </c>
     </row>
     <row r="717">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>22.21808306448784</v>
+        <v>20.75819490613035</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>20.69504767136681</v>
+        <v>19.42483033084923</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>19.47963537042884</v>
+        <v>18.25588087430695</v>
       </c>
     </row>
     <row r="722">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>22.79946056566662</v>
+        <v>22.11191331028376</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>22.11983014848891</v>
+        <v>21.47177912898551</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>21.47809059400845</v>
+        <v>20.85057934275608</v>
       </c>
     </row>
     <row r="727">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>31.45638381280593</v>
+        <v>30.25362780025597</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>31.58255228271281</v>
+        <v>31.33082080386568</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>30.31442443998919</v>
+        <v>29.35882471584591</v>
       </c>
     </row>
     <row r="732">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>25.51424830880926</v>
+        <v>25.33448239386959</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>25.29967619410624</v>
+        <v>25.16642997826883</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>25.17735735280481</v>
+        <v>25.03115968627601</v>
       </c>
     </row>
     <row r="737">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>28.71517731570547</v>
+        <v>28.4473227292431</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>28.02739681597377</v>
+        <v>27.81231779968087</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>28.01375279564282</v>
+        <v>27.78161785800448</v>
       </c>
     </row>
     <row r="742">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>14.48183991965202</v>
+        <v>13.38178845553508</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>13.42340113307142</v>
+        <v>12.48976947961717</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>12.51595424747178</v>
+        <v>11.67630480726307</v>
       </c>
     </row>
     <row r="747">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>32.3773435572627</v>
+        <v>30.61437681162156</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>33.27027094793054</v>
+        <v>33.65528256089507</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>31.44459024380929</v>
+        <v>30.06411135891124</v>
       </c>
     </row>
     <row r="752">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>39.65518461275362</v>
+        <v>39.93558568454114</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>39.9386146686677</v>
+        <v>40.23631592743045</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>40.23757201777322</v>
+        <v>40.54081444134808</v>
       </c>
     </row>
     <row r="757">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>62.13249094773106</v>
+        <v>64.94835542875455</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>64.99632940330309</v>
+        <v>67.93339493178523</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>67.97790308437924</v>
+        <v>71.05195889259791</v>
       </c>
     </row>
     <row r="762">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>35.51426030475785</v>
+        <v>37.15634751219013</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>37.12351093021143</v>
+        <v>38.63512732265287</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>38.62187928353851</v>
+        <v>40.07416301577256</v>
       </c>
     </row>
     <row r="767">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>33.73203457367702</v>
+        <v>34.75562178361276</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>34.78665980562212</v>
+        <v>35.84789287767987</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>35.84689434583469</v>
+        <v>36.93716837621145</v>
       </c>
     </row>
     <row r="772">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>31.40541844632881</v>
+        <v>32.36967403084417</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>32.36937592813498</v>
+        <v>33.3561282440624</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>33.37432004882405</v>
+        <v>34.39715787156558</v>
       </c>
     </row>
     <row r="777">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>20.9527183300371</v>
+        <v>19.40951367106146</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>19.37873711929982</v>
+        <v>17.96119189673832</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>18.02402545370407</v>
+        <v>16.70137079331244</v>
       </c>
     </row>
     <row r="782">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>7.847484796750083</v>
+        <v>6.793363639901802</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>6.844111157123533</v>
+        <v>5.975569048201322</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>6.012118498409304</v>
+        <v>5.267422807124791</v>
       </c>
     </row>
     <row r="787">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>15.61173810856123</v>
+        <v>14.58035290798425</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>14.60197453682883</v>
+        <v>13.63760024972579</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>13.65793586099244</v>
+        <v>12.75585442526728</v>
       </c>
     </row>
     <row r="792">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>15.7905695449488</v>
+        <v>14.40436348013628</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>14.44552673338766</v>
+        <v>13.20646747913418</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>13.24051848226971</v>
+        <v>12.11072448753868</v>
       </c>
     </row>
     <row r="797">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>11.99082360192685</v>
+        <v>10.44025576604588</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>10.50160307118419</v>
+        <v>9.143197895968759</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>9.196911501829746</v>
+        <v>8.007280843474598</v>
       </c>
     </row>
     <row r="802">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>32.46916842011671</v>
+        <v>31.97756565538718</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>31.9255879481072</v>
+        <v>31.44731996334009</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>31.47550508058684</v>
+        <v>31.00162962303323</v>
       </c>
     </row>
     <row r="807">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>9.335308363432484</v>
+        <v>8.070694443290504</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>8.122820227114705</v>
+        <v>7.031436474153993</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>7.076110056345651</v>
+        <v>6.126199251592455</v>
       </c>
     </row>
     <row r="812">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>59.33759470558687</v>
+        <v>61.60413775513521</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>61.60271495742603</v>
+        <v>64.01621926424635</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>64.05690599882075</v>
+        <v>66.55036097708071</v>
       </c>
     </row>
     <row r="817">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>25.30211709514647</v>
+        <v>22.99663918839759</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>23.14856165287367</v>
+        <v>21.4018830166145</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>21.49668436337882</v>
+        <v>20.09153088512436</v>
       </c>
     </row>
     <row r="822">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>21.07514492364075</v>
+        <v>19.634158845319</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>19.66117625274871</v>
+        <v>18.28755370169141</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>18.31685760062677</v>
+        <v>17.02886025486991</v>
       </c>
     </row>
     <row r="827">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>8.553454239804161</v>
+        <v>7.897022123197207</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>7.953910477837323</v>
+        <v>7.303125568497027</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>7.307400127930957</v>
+        <v>6.722052692098638</v>
       </c>
     </row>
     <row r="832">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>31.28011344107007</v>
+        <v>31.16102033738667</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>31.17238990234314</v>
+        <v>31.017764028211</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>31.01588598922829</v>
+        <v>30.86887360208721</v>
       </c>
     </row>
     <row r="837">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>23.58326690040096</v>
+        <v>22.74620561008568</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>22.75587747201758</v>
+        <v>21.94818343032993</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>21.95751596708059</v>
+        <v>21.17815886082614</v>
       </c>
     </row>
     <row r="842">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>19.73032004688286</v>
+        <v>18.97063275008433</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>18.980137470443</v>
+        <v>18.2492822226832</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>18.25842524052885</v>
+        <v>17.55536074881902</v>
       </c>
     </row>
     <row r="847">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>16.41138857736394</v>
+        <v>15.61124662223461</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>15.64065454369698</v>
+        <v>14.85311407051482</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>14.86138645264563</v>
+        <v>14.11979866518745</v>
       </c>
     </row>
     <row r="852">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>35.46326720924878</v>
+        <v>35.93843302093253</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>35.94305227998675</v>
+        <v>36.42525360747691</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>36.42600978566469</v>
+        <v>36.91434272858462</v>
       </c>
     </row>
     <row r="857">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>7.767202855516781</v>
+        <v>6.213710767273667</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>6.334346220485057</v>
+        <v>5.245495972457523</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>5.317586817412248</v>
+        <v>4.493553712505555</v>
       </c>
     </row>
     <row r="862">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>16.42363105432658</v>
+        <v>14.8172231836658</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>14.54833932880407</v>
+        <v>13.11822829578661</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>13.31676592661807</v>
+        <v>12.0148463004018</v>
       </c>
     </row>
     <row r="867">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>49.47902904759535</v>
+        <v>60.15677019216216</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>59.55049686994689</v>
+        <v>68.49820440782894</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>67.93633155052586</v>
+        <v>75.15402005158649</v>
       </c>
     </row>
     <row r="872">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>7.866655355400622</v>
+        <v>6.565256434534563</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>6.80523674693925</v>
+        <v>5.732689296340193</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>5.687069645087828</v>
+        <v>4.763263204388728</v>
       </c>
     </row>
     <row r="877">
@@ -11787,7 +11787,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>28.03789666674616</v>
+        <v>26.85509021274791</v>
       </c>
     </row>
     <row r="880">
@@ -11800,7 +11800,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>26.55002332630876</v>
+        <v>25.65089866296693</v>
       </c>
     </row>
     <row r="881">
@@ -11813,7 +11813,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>25.77809392157731</v>
+        <v>24.82829288901709</v>
       </c>
     </row>
     <row r="882">
@@ -11852,7 +11852,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>25.37833075373211</v>
+        <v>25.1320447943707</v>
       </c>
     </row>
     <row r="885">
@@ -11865,7 +11865,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>25.12581159066804</v>
+        <v>24.89712320166215</v>
       </c>
     </row>
     <row r="886">
@@ -11878,7 +11878,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>24.89947701276564</v>
+        <v>24.66926304226407</v>
       </c>
     </row>
     <row r="887">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>18.18892210384314</v>
+        <v>18.25081219951828</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>19.70155825410656</v>
+        <v>20.81558523761979</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>19.71244318520029</v>
+        <v>20.07093211846281</v>
       </c>
     </row>
     <row r="892">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>26.12934623841019</v>
+        <v>25.39694869406268</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>25.40204112089662</v>
+        <v>24.6894121645512</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>24.69694506138529</v>
+        <v>24.00447432554199</v>
       </c>
     </row>
     <row r="897">
@@ -12047,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>31.70428716548118</v>
+        <v>32.27068489195608</v>
       </c>
     </row>
     <row r="900">
@@ -12060,7 +12060,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>32.66985289818041</v>
+        <v>33.60247919180182</v>
       </c>
     </row>
     <row r="901">
@@ -12073,7 +12073,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>33.25573636505401</v>
+        <v>33.89404501140411</v>
       </c>
     </row>
     <row r="902">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>36.704028030699</v>
+        <v>43.24785855318964</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>43.68604397737244</v>
+        <v>51.47360317943495</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>51.99511518692272</v>
+        <v>61.26388382814356</v>
       </c>
     </row>
     <row r="907">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>31.6184670324769</v>
+        <v>30.73110282970854</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>30.75703158042639</v>
+        <v>29.97570358052983</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>29.98974961588317</v>
+        <v>29.26244243741114</v>
       </c>
     </row>
     <row r="912">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>23.63934006214506</v>
+        <v>23.61008683111009</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>23.59074670973469</v>
+        <v>23.59194406359635</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>23.59736767903585</v>
+        <v>23.59007214240111</v>
       </c>
     </row>
     <row r="917">
@@ -12307,7 +12307,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>25.93634844578948</v>
+        <v>26.82780038620524</v>
       </c>
     </row>
     <row r="920">
@@ -12320,7 +12320,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>26.86381522304185</v>
+        <v>27.92442441070421</v>
       </c>
     </row>
     <row r="921">
@@ -12333,7 +12333,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>27.9453948216466</v>
+        <v>29.08395966803035</v>
       </c>
     </row>
     <row r="922">
@@ -12372,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>18.23509664287327</v>
+        <v>16.70888849798705</v>
       </c>
     </row>
     <row r="925">
@@ -12385,7 +12385,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>16.85786557082847</v>
+        <v>15.32295274161641</v>
       </c>
     </row>
     <row r="926">
@@ -12398,7 +12398,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>15.33575031951258</v>
+        <v>13.97540971893429</v>
       </c>
     </row>
     <row r="927">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>39.74209389863075</v>
+        <v>40.0287357518452</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>40.00302672174139</v>
+        <v>40.1391169833308</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>40.13252139633511</v>
+        <v>40.22971145382935</v>
       </c>
     </row>
     <row r="932">
@@ -12502,7 +12502,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>26.56408115465131</v>
+        <v>26.29881707721589</v>
       </c>
     </row>
     <row r="935">
@@ -12515,7 +12515,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>26.34721472239955</v>
+        <v>26.05501482402107</v>
       </c>
     </row>
     <row r="936">
@@ -12528,7 +12528,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>26.03808798063311</v>
+        <v>25.76043204066236</v>
       </c>
     </row>
     <row r="937">
@@ -12567,7 +12567,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>39.17282247121742</v>
+        <v>40.47450290688386</v>
       </c>
     </row>
     <row r="940">
@@ -12580,7 +12580,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>40.27715356745536</v>
+        <v>41.78327924471024</v>
       </c>
     </row>
     <row r="941">
@@ -12593,7 +12593,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>41.88151505757185</v>
+        <v>43.38676302112147</v>
       </c>
     </row>
     <row r="942">
@@ -12632,7 +12632,7 @@
         <v>2026</v>
       </c>
       <c r="D944">
-        <v>5.08868571642819</v>
+        <v>4.326344905838603</v>
       </c>
     </row>
     <row r="945">
@@ -12645,7 +12645,7 @@
         <v>2027</v>
       </c>
       <c r="D945">
-        <v>4.375314830141746</v>
+        <v>3.84365840170145</v>
       </c>
     </row>
     <row r="946">
@@ -12658,7 +12658,7 @@
         <v>2028</v>
       </c>
       <c r="D946">
-        <v>3.868306115600613</v>
+        <v>3.434915039261785</v>
       </c>
     </row>
     <row r="947">
@@ -12697,7 +12697,7 @@
         <v>2026</v>
       </c>
       <c r="D949">
-        <v>25.60007973744524</v>
+        <v>25.90710493819296</v>
       </c>
     </row>
     <row r="950">
@@ -12710,7 +12710,7 @@
         <v>2027</v>
       </c>
       <c r="D950">
-        <v>25.92814005324923</v>
+        <v>26.34946958944805</v>
       </c>
     </row>
     <row r="951">
@@ -12723,7 +12723,7 @@
         <v>2028</v>
       </c>
       <c r="D951">
-        <v>26.35708375306271</v>
+        <v>26.8146767315471</v>
       </c>
     </row>
     <row r="952">
@@ -12762,7 +12762,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>50.52621874628153</v>
+        <v>51.53222438322526</v>
       </c>
     </row>
     <row r="955">
@@ -12775,7 +12775,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>51.92506683577657</v>
+        <v>53.10974076106272</v>
       </c>
     </row>
     <row r="956">
@@ -12788,7 +12788,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>52.87794773886733</v>
+        <v>53.99187807231402</v>
       </c>
     </row>
     <row r="957">
@@ -12827,7 +12827,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>31.33772415376363</v>
+        <v>30.4798184206446</v>
       </c>
     </row>
     <row r="960">
@@ -12840,7 +12840,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>31.12097988365803</v>
+        <v>30.64236139308771</v>
       </c>
     </row>
     <row r="961">
@@ -12853,7 +12853,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>30.2011180414292</v>
+        <v>29.48117431055529</v>
       </c>
     </row>
     <row r="962">
@@ -12892,7 +12892,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>51.66458242344359</v>
+        <v>54.562882181989</v>
       </c>
     </row>
     <row r="965">
@@ -12905,7 +12905,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>54.61918884252435</v>
+        <v>57.68388067926693</v>
       </c>
     </row>
     <row r="966">
@@ -12918,7 +12918,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>57.74338851581194</v>
+        <v>60.98340268617989</v>
       </c>
     </row>
     <row r="967">
@@ -12957,7 +12957,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>67.56696201401346</v>
+        <v>72.44640151644438</v>
       </c>
     </row>
     <row r="970">
@@ -12970,7 +12970,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>72.55440479343764</v>
+        <v>77.79809629790203</v>
       </c>
     </row>
     <row r="971">
@@ -12983,7 +12983,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>77.93768947704106</v>
+        <v>83.56857061677678</v>
       </c>
     </row>
     <row r="972">
@@ -13022,7 +13022,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>14.52128253916927</v>
+        <v>14.27423424507698</v>
       </c>
     </row>
     <row r="975">
@@ -13035,7 +13035,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>13.981073639527</v>
+        <v>13.56510098980592</v>
       </c>
     </row>
     <row r="976">
@@ -13048,7 +13048,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>13.77976606369018</v>
+        <v>13.49996295618763</v>
       </c>
     </row>
     <row r="977">
@@ -13087,7 +13087,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>38.45095575763961</v>
+        <v>40.00715884358832</v>
       </c>
     </row>
     <row r="980">
@@ -13100,7 +13100,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>38.29320586779193</v>
+        <v>38.1476814296111</v>
       </c>
     </row>
     <row r="981">
@@ -13113,7 +13113,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>39.86676241020169</v>
+        <v>41.44544695740563</v>
       </c>
     </row>
     <row r="982">
@@ -13152,7 +13152,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>25.8297430313906</v>
+        <v>26.02985100929962</v>
       </c>
     </row>
     <row r="985">
@@ -13165,7 +13165,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>26.11109492449257</v>
+        <v>26.23859739349059</v>
       </c>
     </row>
     <row r="986">
@@ -13178,7 +13178,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>26.21118263474224</v>
+        <v>26.36509950143653</v>
       </c>
     </row>
     <row r="987">
@@ -13217,7 +13217,7 @@
         <v>2026</v>
       </c>
       <c r="D989">
-        <v>11.74851722042898</v>
+        <v>11.26611498766271</v>
       </c>
     </row>
     <row r="990">
@@ -13230,7 +13230,7 @@
         <v>2027</v>
       </c>
       <c r="D990">
-        <v>11.25326628094298</v>
+        <v>10.78432465872796</v>
       </c>
     </row>
     <row r="991">
@@ -13243,7 +13243,7 @@
         <v>2028</v>
       </c>
       <c r="D991">
-        <v>10.80221626916337</v>
+        <v>10.35620916109944</v>
       </c>
     </row>
     <row r="992">
@@ -13282,7 +13282,7 @@
         <v>2026</v>
       </c>
       <c r="D994">
-        <v>29.51629022030066</v>
+        <v>31.14760880109298</v>
       </c>
     </row>
     <row r="995">
@@ -13295,7 +13295,7 @@
         <v>2027</v>
       </c>
       <c r="D995">
-        <v>31.07338017504597</v>
+        <v>32.34330254984154</v>
       </c>
     </row>
     <row r="996">
@@ -13308,7 +13308,7 @@
         <v>2028</v>
       </c>
       <c r="D996">
-        <v>32.32303625810874</v>
+        <v>33.47819742339168</v>
       </c>
     </row>
     <row r="997">
@@ -13347,7 +13347,7 @@
         <v>2026</v>
       </c>
       <c r="D999">
-        <v>13.72145446450394</v>
+        <v>14.30248369354969</v>
       </c>
     </row>
     <row r="1000">
@@ -13360,7 +13360,7 @@
         <v>2027</v>
       </c>
       <c r="D1000">
-        <v>14.31091989180762</v>
+        <v>14.91680617332754</v>
       </c>
     </row>
     <row r="1001">
@@ -13373,7 +13373,7 @@
         <v>2028</v>
       </c>
       <c r="D1001">
-        <v>14.9256015718948</v>
+        <v>15.55751484880718</v>
       </c>
     </row>
     <row r="1002">
@@ -13412,7 +13412,7 @@
         <v>2026</v>
       </c>
       <c r="D1004">
-        <v>33.68889457479577</v>
+        <v>34.0450800211597</v>
       </c>
     </row>
     <row r="1005">
@@ -13425,7 +13425,7 @@
         <v>2027</v>
       </c>
       <c r="D1005">
-        <v>33.98844395115766</v>
+        <v>34.41073896999693</v>
       </c>
     </row>
     <row r="1006">
@@ -13438,7 +13438,7 @@
         <v>2028</v>
       </c>
       <c r="D1006">
-        <v>34.43153583755413</v>
+        <v>34.83878852150578</v>
       </c>
     </row>
     <row r="1007">
@@ -13477,7 +13477,7 @@
         <v>2026</v>
       </c>
       <c r="D1009">
-        <v>11.32207044423302</v>
+        <v>11.73974739909004</v>
       </c>
     </row>
     <row r="1010">
@@ -13490,7 +13490,7 @@
         <v>2027</v>
       </c>
       <c r="D1010">
-        <v>11.74735777814825</v>
+        <v>12.1721983348936</v>
       </c>
     </row>
     <row r="1011">
@@ -13503,7 +13503,7 @@
         <v>2028</v>
       </c>
       <c r="D1011">
-        <v>12.17698946668968</v>
+        <v>12.61902266608541</v>
       </c>
     </row>
     <row r="1012">
@@ -13542,7 +13542,7 @@
         <v>2026</v>
       </c>
       <c r="D1014">
-        <v>37.99870947873205</v>
+        <v>37.25251469898213</v>
       </c>
     </row>
     <row r="1015">
@@ -13555,7 +13555,7 @@
         <v>2027</v>
       </c>
       <c r="D1015">
-        <v>37.26336707565267</v>
+        <v>36.51863306253973</v>
       </c>
     </row>
     <row r="1016">
@@ -13568,7 +13568,7 @@
         <v>2028</v>
       </c>
       <c r="D1016">
-        <v>36.52212499408596</v>
+        <v>35.79522722073601</v>
       </c>
     </row>
     <row r="1017">
@@ -13607,7 +13607,7 @@
         <v>2026</v>
       </c>
       <c r="D1019">
-        <v>30.82463520384758</v>
+        <v>31.26580194986444</v>
       </c>
     </row>
     <row r="1020">
@@ -13620,7 +13620,7 @@
         <v>2027</v>
       </c>
       <c r="D1020">
-        <v>31.26844626541014</v>
+        <v>31.70680563285319</v>
       </c>
     </row>
     <row r="1021">
@@ -13633,7 +13633,7 @@
         <v>2028</v>
       </c>
       <c r="D1021">
-        <v>31.70884246294444</v>
+        <v>32.1539198061157</v>
       </c>
     </row>
     <row r="1022">
@@ -13672,7 +13672,7 @@
         <v>2026</v>
       </c>
       <c r="D1024">
-        <v>5.79805142243103</v>
+        <v>5.932890019178609</v>
       </c>
     </row>
     <row r="1025">
@@ -13685,7 +13685,7 @@
         <v>2027</v>
       </c>
       <c r="D1025">
-        <v>6.005269733082602</v>
+        <v>6.098049208603447</v>
       </c>
     </row>
     <row r="1026">
@@ -13698,7 +13698,7 @@
         <v>2028</v>
       </c>
       <c r="D1026">
-        <v>6.071721732209707</v>
+        <v>6.184225968847066</v>
       </c>
     </row>
     <row r="1027">
@@ -13737,7 +13737,7 @@
         <v>2026</v>
       </c>
       <c r="D1029">
-        <v>16.23069010394989</v>
+        <v>15.67137682359349</v>
       </c>
     </row>
     <row r="1030">
@@ -13750,7 +13750,7 @@
         <v>2027</v>
       </c>
       <c r="D1030">
-        <v>15.64188787945405</v>
+        <v>15.14400742688394</v>
       </c>
     </row>
     <row r="1031">
@@ -13763,7 +13763,7 @@
         <v>2028</v>
       </c>
       <c r="D1031">
-        <v>15.1601539801551</v>
+        <v>14.66507768998785</v>
       </c>
     </row>
     <row r="1032">
@@ -13802,7 +13802,7 @@
         <v>2026</v>
       </c>
       <c r="D1034">
-        <v>8.548577485607284</v>
+        <v>7.590420361427286</v>
       </c>
     </row>
     <row r="1035">
@@ -13815,7 +13815,7 @@
         <v>2027</v>
       </c>
       <c r="D1035">
-        <v>7.623540233964019</v>
+        <v>6.769822494155562</v>
       </c>
     </row>
     <row r="1036">
@@ -13828,7 +13828,7 @@
         <v>2028</v>
       </c>
       <c r="D1036">
-        <v>6.799395021913107</v>
+        <v>6.037942210156475</v>
       </c>
     </row>
     <row r="1037">
@@ -13867,7 +13867,7 @@
         <v>2026</v>
       </c>
       <c r="D1039">
-        <v>4.624073278753215</v>
+        <v>4.367259581369906</v>
       </c>
     </row>
     <row r="1040">
@@ -13880,7 +13880,7 @@
         <v>2027</v>
       </c>
       <c r="D1040">
-        <v>4.40676813209148</v>
+        <v>4.129645551316472</v>
       </c>
     </row>
     <row r="1041">
@@ -13893,7 +13893,7 @@
         <v>2028</v>
       </c>
       <c r="D1041">
-        <v>4.124076881789313</v>
+        <v>3.875325512681564</v>
       </c>
     </row>
     <row r="1042">
@@ -13932,7 +13932,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>7.697396991713291</v>
+        <v>7.399069933813712</v>
       </c>
     </row>
     <row r="1045">
@@ -13945,7 +13945,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>7.535163243689877</v>
+        <v>7.305333696562957</v>
       </c>
     </row>
     <row r="1046">
@@ -13958,7 +13958,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>7.222627995097029</v>
+        <v>6.963480354914418</v>
       </c>
     </row>
     <row r="1047">
@@ -13997,7 +13997,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>27.90365088443832</v>
+        <v>30.24657416194066</v>
       </c>
     </row>
     <row r="1050">
@@ -14010,7 +14010,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>31.47577954218002</v>
+        <v>34.82306704263981</v>
       </c>
     </row>
     <row r="1051">
@@ -14023,7 +14023,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>34.10356736509993</v>
+        <v>37.24106089071931</v>
       </c>
     </row>
     <row r="1052">
@@ -14062,7 +14062,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>15.67803417098123</v>
+        <v>16.85458932138134</v>
       </c>
     </row>
     <row r="1055">
@@ -14075,7 +14075,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>17.54351078039171</v>
+        <v>19.44013442289825</v>
       </c>
     </row>
     <row r="1056">
@@ -14088,7 +14088,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>18.91188615207658</v>
+        <v>20.44093471195013</v>
       </c>
     </row>
     <row r="1057">
@@ -14127,7 +14127,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>0.7742827394178095</v>
+        <v>0.6906284831153089</v>
       </c>
     </row>
     <row r="1060">
@@ -14140,7 +14140,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>0.6678074373524465</v>
+        <v>0.5838513863582</v>
       </c>
     </row>
     <row r="1061">
@@ -14153,7 +14153,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>0.6032264034774634</v>
+        <v>0.5351993409588814</v>
       </c>
     </row>
     <row r="1062">
@@ -14192,7 +14192,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>37.20189329296409</v>
+        <v>63.75392619409948</v>
       </c>
     </row>
     <row r="1065">
@@ -14205,7 +14205,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>74.36144239828299</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1066">
@@ -14257,7 +14257,7 @@
         <v>2026</v>
       </c>
       <c r="D1069">
-        <v>56.80289728303262</v>
+        <v>69.36168540700169</v>
       </c>
     </row>
     <row r="1070">
@@ -14270,7 +14270,7 @@
         <v>2027</v>
       </c>
       <c r="D1070">
-        <v>69.55397192024002</v>
+        <v>82.70363898544213</v>
       </c>
     </row>
     <row r="1071">
@@ -14283,7 +14283,7 @@
         <v>2028</v>
       </c>
       <c r="D1071">
-        <v>82.91655864092728</v>
+        <v>96.68435153033802</v>
       </c>
     </row>
     <row r="1072">
@@ -14322,7 +14322,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>24.71785262491881</v>
+        <v>23.99408031607997</v>
       </c>
     </row>
     <row r="1075">
@@ -14335,7 +14335,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>24.00169183654974</v>
+        <v>23.2982776141864</v>
       </c>
     </row>
     <row r="1076">
@@ -14348,7 +14348,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>23.30478667275024</v>
+        <v>22.62200208798437</v>
       </c>
     </row>
     <row r="1077">
@@ -14387,7 +14387,7 @@
         <v>2026</v>
       </c>
       <c r="D1079">
-        <v>43.42126953204803</v>
+        <v>45.96556987084413</v>
       </c>
     </row>
     <row r="1080">
@@ -14400,7 +14400,7 @@
         <v>2027</v>
       </c>
       <c r="D1080">
-        <v>46.02146987161396</v>
+        <v>48.68484503620467</v>
       </c>
     </row>
     <row r="1081">
@@ -14413,7 +14413,7 @@
         <v>2028</v>
       </c>
       <c r="D1081">
-        <v>48.73768838992449</v>
+        <v>51.56265026272466</v>
       </c>
     </row>
     <row r="1082">
@@ -14452,7 +14452,7 @@
         <v>2026</v>
       </c>
       <c r="D1084">
-        <v>20.15638757434102</v>
+        <v>20.40240255642125</v>
       </c>
     </row>
     <row r="1085">
@@ -14465,7 +14465,7 @@
         <v>2027</v>
       </c>
       <c r="D1085">
-        <v>18.37857072242722</v>
+        <v>16.96037503876923</v>
       </c>
     </row>
     <row r="1086">
@@ -14478,7 +14478,7 @@
         <v>2028</v>
       </c>
       <c r="D1086">
-        <v>18.70805845029849</v>
+        <v>18.761397755705</v>
       </c>
     </row>
     <row r="1087">
@@ -14517,7 +14517,7 @@
         <v>2026</v>
       </c>
       <c r="D1089">
-        <v>40.07779550232329</v>
+        <v>47.79082085315376</v>
       </c>
     </row>
     <row r="1090">
@@ -14530,7 +14530,7 @@
         <v>2027</v>
       </c>
       <c r="D1090">
-        <v>48.35385614781257</v>
+        <v>57.65961965352113</v>
       </c>
     </row>
     <row r="1091">
@@ -14543,7 +14543,7 @@
         <v>2028</v>
       </c>
       <c r="D1091">
-        <v>58.33892156606964</v>
+        <v>69.56632419153404</v>
       </c>
     </row>
     <row r="1092">
@@ -14582,7 +14582,7 @@
         <v>2026</v>
       </c>
       <c r="D1094">
-        <v>16.18660415867778</v>
+        <v>17.73712816558944</v>
       </c>
     </row>
     <row r="1095">
@@ -14595,7 +14595,7 @@
         <v>2027</v>
       </c>
       <c r="D1095">
-        <v>16.41876091158563</v>
+        <v>16.74602552917507</v>
       </c>
     </row>
     <row r="1096">
@@ -14608,7 +14608,7 @@
         <v>2028</v>
       </c>
       <c r="D1096">
-        <v>18.04428174717897</v>
+        <v>19.64969154677241</v>
       </c>
     </row>
     <row r="1097">
@@ -14647,7 +14647,7 @@
         <v>2026</v>
       </c>
       <c r="D1099">
-        <v>11.6885018341813</v>
+        <v>11.42971959259184</v>
       </c>
     </row>
     <row r="1100">
@@ -14660,7 +14660,7 @@
         <v>2027</v>
       </c>
       <c r="D1100">
-        <v>11.99945912890018</v>
+        <v>12.14278219372891</v>
       </c>
     </row>
     <row r="1101">
@@ -14673,7 +14673,7 @@
         <v>2028</v>
       </c>
       <c r="D1101">
-        <v>11.7047437928736</v>
+        <v>11.54172959230006</v>
       </c>
     </row>
     <row r="1102">
@@ -14712,7 +14712,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>6.052414703479209</v>
+        <v>5.583048250532532</v>
       </c>
     </row>
     <row r="1105">
@@ -14725,7 +14725,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>6.229786353320087</v>
+        <v>6.168735686700566</v>
       </c>
     </row>
     <row r="1106">
@@ -14738,7 +14738,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>5.710757908353838</v>
+        <v>5.380489787828417</v>
       </c>
     </row>
     <row r="1107">
@@ -14777,7 +14777,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>56.98570591448867</v>
+        <v>58.35457497716378</v>
       </c>
     </row>
     <row r="1110">
@@ -14790,7 +14790,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>58.48733496776066</v>
+        <v>59.95007314558993</v>
       </c>
     </row>
     <row r="1111">
@@ -14803,7 +14803,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>59.88210635135753</v>
+        <v>61.34167093131887</v>
       </c>
     </row>
     <row r="1112">
@@ -14842,7 +14842,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>1.947940109152974</v>
+        <v>1.673653718866793</v>
       </c>
     </row>
     <row r="1115">
@@ -14855,7 +14855,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>1.90080195992898</v>
+        <v>1.77432719912766</v>
       </c>
     </row>
     <row r="1116">
@@ -14868,7 +14868,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>1.625321744590048</v>
+        <v>1.427984315775691</v>
       </c>
     </row>
     <row r="1117">
@@ -14907,7 +14907,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>33.12491493289144</v>
+        <v>37.71337863521274</v>
       </c>
     </row>
     <row r="1120">
@@ -14920,7 +14920,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>37.23951038612299</v>
+        <v>41.81985676496124</v>
       </c>
     </row>
     <row r="1121">
@@ -14933,7 +14933,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>42.64961999226444</v>
+        <v>48.41562457661934</v>
       </c>
     </row>
     <row r="1122">
@@ -14972,7 +14972,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>2.376543203869088</v>
+        <v>2.019001940895744</v>
       </c>
     </row>
     <row r="1125">
@@ -14985,7 +14985,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>1.722187208916599</v>
+        <v>1.294598476722681</v>
       </c>
     </row>
     <row r="1126">
@@ -14998,7 +14998,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>1.530953842390403</v>
+        <v>1.279261109552783</v>
       </c>
     </row>
     <row r="1127">
@@ -15037,7 +15037,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>2.921219376516573</v>
+        <v>2.510101574860815</v>
       </c>
     </row>
     <row r="1130">
@@ -15050,7 +15050,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>2.527707147000143</v>
+        <v>2.171599175438395</v>
       </c>
     </row>
     <row r="1131">
@@ -15063,7 +15063,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>2.186815123092568</v>
+        <v>1.878744618978493</v>
       </c>
     </row>
     <row r="1132">
@@ -15102,7 +15102,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>14.15388373490545</v>
+        <v>12.23633227555537</v>
       </c>
     </row>
     <row r="1135">
@@ -15115,7 +15115,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>14.1550540388968</v>
+        <v>14.04302174879583</v>
       </c>
     </row>
     <row r="1136">
@@ -15128,7 +15128,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>12.31452637636699</v>
+        <v>10.66422510474978</v>
       </c>
     </row>
     <row r="1137">
@@ -15167,7 +15167,7 @@
         <v>2026</v>
       </c>
       <c r="D1139">
-        <v>40.06741685896663</v>
+        <v>41.55328582420673</v>
       </c>
     </row>
     <row r="1140">
@@ -15180,7 +15180,7 @@
         <v>2027</v>
       </c>
       <c r="D1140">
-        <v>41.47572762684347</v>
+        <v>43.10254303883431</v>
       </c>
     </row>
     <row r="1141">
@@ -15193,7 +15193,7 @@
         <v>2028</v>
       </c>
       <c r="D1141">
-        <v>43.15870308566588</v>
+        <v>44.82028039395657</v>
       </c>
     </row>
     <row r="1142">
@@ -15232,7 +15232,7 @@
         <v>2026</v>
       </c>
       <c r="D1144">
-        <v>62.81762324318318</v>
+        <v>69.10558180079914</v>
       </c>
     </row>
     <row r="1145">
@@ -15245,7 +15245,7 @@
         <v>2027</v>
       </c>
       <c r="D1145">
-        <v>69.26245933082289</v>
+        <v>76.16528235334532</v>
       </c>
     </row>
     <row r="1146">
@@ -15258,7 +15258,7 @@
         <v>2028</v>
       </c>
       <c r="D1146">
-        <v>76.45539163996864</v>
+        <v>84.09531076576144</v>
       </c>
     </row>
     <row r="1147">
@@ -15297,7 +15297,7 @@
         <v>2026</v>
       </c>
       <c r="D1149">
-        <v>24.12529036688058</v>
+        <v>23.11116055749432</v>
       </c>
     </row>
     <row r="1150">
@@ -15310,7 +15310,7 @@
         <v>2027</v>
       </c>
       <c r="D1150">
-        <v>22.73173628995893</v>
+        <v>21.57047938595269</v>
       </c>
     </row>
     <row r="1151">
@@ -15323,7 +15323,7 @@
         <v>2028</v>
       </c>
       <c r="D1151">
-        <v>21.8530467430569</v>
+        <v>20.87750028572367</v>
       </c>
     </row>
     <row r="1152">
@@ -15362,7 +15362,7 @@
         <v>2026</v>
       </c>
       <c r="D1154">
-        <v>33.52554648644021</v>
+        <v>34.54100499767763</v>
       </c>
     </row>
     <row r="1155">
@@ -15375,7 +15375,7 @@
         <v>2027</v>
       </c>
       <c r="D1155">
-        <v>30.81216779865513</v>
+        <v>28.46941105577285</v>
       </c>
     </row>
     <row r="1156">
@@ -15388,7 +15388,7 @@
         <v>2028</v>
       </c>
       <c r="D1156">
-        <v>31.88468831666841</v>
+        <v>32.64364889655477</v>
       </c>
     </row>
     <row r="1157">
@@ -15427,7 +15427,7 @@
         <v>2026</v>
       </c>
       <c r="D1159">
-        <v>33.56354638759669</v>
+        <v>33.31913291684108</v>
       </c>
     </row>
     <row r="1160">
@@ -15440,7 +15440,7 @@
         <v>2027</v>
       </c>
       <c r="D1160">
-        <v>33.44525307062355</v>
+        <v>33.10491451085443</v>
       </c>
     </row>
     <row r="1161">
@@ -15453,7 +15453,7 @@
         <v>2028</v>
       </c>
       <c r="D1161">
-        <v>33.06132972738084</v>
+        <v>32.75994175444703</v>
       </c>
     </row>
     <row r="1162">
@@ -15492,7 +15492,7 @@
         <v>2026</v>
       </c>
       <c r="D1164">
-        <v>7.830877543467188</v>
+        <v>7.263831404426877</v>
       </c>
     </row>
     <row r="1165">
@@ -15505,7 +15505,7 @@
         <v>2027</v>
       </c>
       <c r="D1165">
-        <v>7.275164621485106</v>
+        <v>6.727792205096545</v>
       </c>
     </row>
     <row r="1166">
@@ -15518,7 +15518,7 @@
         <v>2028</v>
       </c>
       <c r="D1166">
-        <v>6.740575934812699</v>
+        <v>6.230104194914673</v>
       </c>
     </row>
     <row r="1167">
@@ -15557,7 +15557,7 @@
         <v>2026</v>
       </c>
       <c r="D1169">
-        <v>13.73408287664323</v>
+        <v>13.42077231308689</v>
       </c>
     </row>
     <row r="1170">
@@ -15570,7 +15570,7 @@
         <v>2027</v>
       </c>
       <c r="D1170">
-        <v>13.42317182414575</v>
+        <v>13.11656358472777</v>
       </c>
     </row>
     <row r="1171">
@@ -15583,7 +15583,7 @@
         <v>2028</v>
       </c>
       <c r="D1171">
-        <v>13.11885778355662</v>
+        <v>12.81923745285519</v>
       </c>
     </row>
     <row r="1172">
@@ -15622,7 +15622,7 @@
         <v>2026</v>
       </c>
       <c r="D1174">
-        <v>32.39285741647834</v>
+        <v>34.49173572189166</v>
       </c>
     </row>
     <row r="1175">
@@ -15635,7 +15635,7 @@
         <v>2027</v>
       </c>
       <c r="D1175">
-        <v>34.62700508303627</v>
+        <v>36.83121681160146</v>
       </c>
     </row>
     <row r="1176">
@@ -15648,7 +15648,7 @@
         <v>2028</v>
       </c>
       <c r="D1176">
-        <v>36.84262986932218</v>
+        <v>39.20493707447343</v>
       </c>
     </row>
     <row r="1177">
@@ -15687,7 +15687,7 @@
         <v>2026</v>
       </c>
       <c r="D1179">
-        <v>43.4608804727072</v>
+        <v>44.77225090452657</v>
       </c>
     </row>
     <row r="1180">
@@ -15700,7 +15700,7 @@
         <v>2027</v>
       </c>
       <c r="D1180">
-        <v>44.63115380955551</v>
+        <v>46.06399980805666</v>
       </c>
     </row>
     <row r="1181">
@@ -15713,7 +15713,7 @@
         <v>2028</v>
       </c>
       <c r="D1181">
-        <v>46.14180814050503</v>
+        <v>47.58917370893187</v>
       </c>
     </row>
     <row r="1182">
@@ -15752,7 +15752,7 @@
         <v>2026</v>
       </c>
       <c r="D1184">
-        <v>24.89697939396241</v>
+        <v>24.01258558528456</v>
       </c>
     </row>
     <row r="1185">
@@ -15765,7 +15765,7 @@
         <v>2027</v>
       </c>
       <c r="D1185">
-        <v>24.02181588780769</v>
+        <v>23.15500168904694</v>
       </c>
     </row>
     <row r="1186">
@@ -15778,7 +15778,7 @@
         <v>2028</v>
       </c>
       <c r="D1186">
-        <v>23.16506543689602</v>
+        <v>22.32760903635656</v>
       </c>
     </row>
     <row r="1187">
@@ -15817,7 +15817,7 @@
         <v>2026</v>
       </c>
       <c r="D1189">
-        <v>30.67636079775884</v>
+        <v>30.30864448616297</v>
       </c>
     </row>
     <row r="1190">
@@ -15830,7 +15830,7 @@
         <v>2027</v>
       </c>
       <c r="D1190">
-        <v>30.30836016755316</v>
+        <v>29.95614545007921</v>
       </c>
     </row>
     <row r="1191">
@@ -15843,7 +15843,7 @@
         <v>2028</v>
       </c>
       <c r="D1191">
-        <v>29.95769664097615</v>
+        <v>29.60829998668627</v>
       </c>
     </row>
     <row r="1192">
@@ -15882,7 +15882,7 @@
         <v>2026</v>
       </c>
       <c r="D1194">
-        <v>16.83128046906038</v>
+        <v>18.01090930431777</v>
       </c>
     </row>
     <row r="1195">
@@ -15895,7 +15895,7 @@
         <v>2027</v>
       </c>
       <c r="D1195">
-        <v>18.00547149279874</v>
+        <v>19.33462964841409</v>
       </c>
     </row>
     <row r="1196">
@@ -15908,7 +15908,7 @@
         <v>2028</v>
       </c>
       <c r="D1196">
-        <v>19.37865056733441</v>
+        <v>20.79041274927138</v>
       </c>
     </row>
     <row r="1197">
@@ -15947,7 +15947,7 @@
         <v>2026</v>
       </c>
       <c r="D1199">
-        <v>0.06353231304761014</v>
+        <v>0.04057643848349791</v>
       </c>
     </row>
     <row r="1200">
@@ -15960,7 +15960,7 @@
         <v>2027</v>
       </c>
       <c r="D1200">
-        <v>0.04272968418116468</v>
+        <v>0.02750044972959656</v>
       </c>
     </row>
     <row r="1201">
@@ -15973,7 +15973,7 @@
         <v>2028</v>
       </c>
       <c r="D1201">
-        <v>0.02891567371408571</v>
+        <v>0.01867013292916267</v>
       </c>
     </row>
     <row r="1202">
@@ -16012,7 +16012,7 @@
         <v>2026</v>
       </c>
       <c r="D1204">
-        <v>9.848057667347517</v>
+        <v>9.973742827654675</v>
       </c>
     </row>
     <row r="1205">
@@ -16025,7 +16025,7 @@
         <v>2027</v>
       </c>
       <c r="D1205">
-        <v>9.885543565717969</v>
+        <v>10.05157121992406</v>
       </c>
     </row>
     <row r="1206">
@@ -16038,7 +16038,7 @@
         <v>2028</v>
       </c>
       <c r="D1206">
-        <v>10.08950736465136</v>
+        <v>10.24320804637534</v>
       </c>
     </row>
     <row r="1207">
@@ -16077,7 +16077,7 @@
         <v>2026</v>
       </c>
       <c r="D1209">
-        <v>57.04946367759936</v>
+        <v>62.19791695295739</v>
       </c>
     </row>
     <row r="1210">
@@ -16090,7 +16090,7 @@
         <v>2027</v>
       </c>
       <c r="D1210">
-        <v>59.09038369245977</v>
+        <v>61.51371583033238</v>
       </c>
     </row>
     <row r="1211">
@@ -16103,7 +16103,7 @@
         <v>2028</v>
       </c>
       <c r="D1211">
-        <v>64.58246334997192</v>
+        <v>70.03575726662598</v>
       </c>
     </row>
     <row r="1212">
@@ -16142,7 +16142,7 @@
         <v>2026</v>
       </c>
       <c r="D1214">
-        <v>3.372232279800649</v>
+        <v>3.213590722997295</v>
       </c>
     </row>
     <row r="1215">
@@ -16155,7 +16155,7 @@
         <v>2027</v>
       </c>
       <c r="D1215">
-        <v>3.045739426158056</v>
+        <v>2.856548894037632</v>
       </c>
     </row>
     <row r="1216">
@@ -16168,7 +16168,7 @@
         <v>2028</v>
       </c>
       <c r="D1216">
-        <v>2.958795789182518</v>
+        <v>2.806247750512629</v>
       </c>
     </row>
     <row r="1217">
@@ -16207,7 +16207,7 @@
         <v>2026</v>
       </c>
       <c r="D1219">
-        <v>38.79553133469427</v>
+        <v>42.45499597859298</v>
       </c>
     </row>
     <row r="1220">
@@ -16220,7 +16220,7 @@
         <v>2027</v>
       </c>
       <c r="D1220">
-        <v>42.75507043275733</v>
+        <v>46.83964000745792</v>
       </c>
     </row>
     <row r="1221">
@@ -16233,7 +16233,7 @@
         <v>2028</v>
       </c>
       <c r="D1221">
-        <v>46.87086404243112</v>
+        <v>51.31795614124248</v>
       </c>
     </row>
     <row r="1222">
@@ -16272,7 +16272,7 @@
         <v>2026</v>
       </c>
       <c r="D1224">
-        <v>38.21284202517972</v>
+        <v>36.25281759656003</v>
       </c>
     </row>
     <row r="1225">
@@ -16285,7 +16285,7 @@
         <v>2027</v>
       </c>
       <c r="D1225">
-        <v>36.51779522395741</v>
+        <v>34.84864892752959</v>
       </c>
     </row>
     <row r="1226">
@@ -16298,7 +16298,7 @@
         <v>2028</v>
       </c>
       <c r="D1226">
-        <v>34.66938708253275</v>
+        <v>32.90669472350863</v>
       </c>
     </row>
     <row r="1227">
@@ -16337,7 +16337,7 @@
         <v>2026</v>
       </c>
       <c r="D1229">
-        <v>16.99749865038327</v>
+        <v>16.45619398052106</v>
       </c>
     </row>
     <row r="1230">
@@ -16350,7 +16350,7 @@
         <v>2027</v>
       </c>
       <c r="D1230">
-        <v>16.70291992123939</v>
+        <v>16.16283819081796</v>
       </c>
     </row>
     <row r="1231">
@@ -16363,7 +16363,7 @@
         <v>2028</v>
       </c>
       <c r="D1231">
-        <v>16.05315616764959</v>
+        <v>15.54043633160973</v>
       </c>
     </row>
     <row r="1232">
@@ -16402,7 +16402,7 @@
         <v>2026</v>
       </c>
       <c r="D1234">
-        <v>5.142450254360206</v>
+        <v>4.459384119124733</v>
       </c>
     </row>
     <row r="1235">
@@ -16415,7 +16415,7 @@
         <v>2027</v>
       </c>
       <c r="D1235">
-        <v>4.487267064212449</v>
+        <v>3.890236611318232</v>
       </c>
     </row>
     <row r="1236">
@@ -16428,7 +16428,7 @@
         <v>2028</v>
       </c>
       <c r="D1236">
-        <v>3.914442111150186</v>
+        <v>3.393705603007591</v>
       </c>
     </row>
     <row r="1237">
@@ -16467,7 +16467,7 @@
         <v>2026</v>
       </c>
       <c r="D1239">
-        <v>4.168139842722211</v>
+        <v>3.659941509753743</v>
       </c>
     </row>
     <row r="1240">
@@ -16480,7 +16480,7 @@
         <v>2027</v>
       </c>
       <c r="D1240">
-        <v>3.676573630095774</v>
+        <v>3.228571654937802</v>
       </c>
     </row>
     <row r="1241">
@@ -16493,7 +16493,7 @@
         <v>2028</v>
       </c>
       <c r="D1241">
-        <v>3.246406643354398</v>
+        <v>2.850706765371651</v>
       </c>
     </row>
     <row r="1242">
@@ -16532,7 +16532,7 @@
         <v>2026</v>
       </c>
       <c r="D1244">
-        <v>43.95492194690846</v>
+        <v>43.82136618414962</v>
       </c>
     </row>
     <row r="1245">
@@ -16545,7 +16545,7 @@
         <v>2027</v>
       </c>
       <c r="D1245">
-        <v>43.79750514399105</v>
+        <v>43.69617048431872</v>
       </c>
     </row>
     <row r="1246">
@@ -16558,7 +16558,7 @@
         <v>2028</v>
       </c>
       <c r="D1246">
-        <v>43.70345362890061</v>
+        <v>43.59282421823349</v>
       </c>
     </row>
     <row r="1247">
@@ -16597,7 +16597,7 @@
         <v>2026</v>
       </c>
       <c r="D1249">
-        <v>68.8850864298939</v>
+        <v>72.03916277800501</v>
       </c>
     </row>
     <row r="1250">
@@ -16610,7 +16610,7 @@
         <v>2027</v>
       </c>
       <c r="D1250">
-        <v>71.92485728981656</v>
+        <v>74.70143077208239</v>
       </c>
     </row>
     <row r="1251">
@@ -16623,7 +16623,7 @@
         <v>2028</v>
       </c>
       <c r="D1251">
-        <v>74.61568015961551</v>
+        <v>77.1064469287591</v>
       </c>
     </row>
     <row r="1252">
@@ -16662,7 +16662,7 @@
         <v>2026</v>
       </c>
       <c r="D1254">
-        <v>24.03013006087783</v>
+        <v>23.29579633306165</v>
       </c>
     </row>
     <row r="1255">
@@ -16675,7 +16675,7 @@
         <v>2027</v>
       </c>
       <c r="D1255">
-        <v>23.29426271202613</v>
+        <v>22.51508377498802</v>
       </c>
     </row>
     <row r="1256">
@@ -16688,7 +16688,7 @@
         <v>2028</v>
       </c>
       <c r="D1256">
-        <v>22.52174854250414</v>
+        <v>21.75436551946273</v>
       </c>
     </row>
     <row r="1257">
@@ -16727,7 +16727,7 @@
         <v>2026</v>
       </c>
       <c r="D1259">
-        <v>20.92327671969332</v>
+        <v>24.08368152164218</v>
       </c>
     </row>
     <row r="1260">
@@ -16740,7 +16740,7 @@
         <v>2027</v>
       </c>
       <c r="D1260">
-        <v>24.25974069010408</v>
+        <v>27.92410942155021</v>
       </c>
     </row>
     <row r="1261">
@@ -16753,7 +16753,7 @@
         <v>2028</v>
       </c>
       <c r="D1261">
-        <v>28.12824330699374</v>
+        <v>32.37693897778883</v>
       </c>
     </row>
     <row r="1262">
@@ -16792,7 +16792,7 @@
         <v>2026</v>
       </c>
       <c r="D1264">
-        <v>2.015766772995964</v>
+        <v>1.751659886366396</v>
       </c>
     </row>
     <row r="1265">
@@ -16805,7 +16805,7 @@
         <v>2027</v>
       </c>
       <c r="D1265">
-        <v>1.830473727965954</v>
+        <v>1.651533501832778</v>
       </c>
     </row>
     <row r="1266">
@@ -16818,7 +16818,7 @@
         <v>2028</v>
       </c>
       <c r="D1266">
-        <v>1.597689106009583</v>
+        <v>1.389873929829576</v>
       </c>
     </row>
     <row r="1267">
@@ -16857,7 +16857,7 @@
         <v>2026</v>
       </c>
       <c r="D1269">
-        <v>41.06254730032511</v>
+        <v>42.45760448932747</v>
       </c>
     </row>
     <row r="1270">
@@ -16870,7 +16870,7 @@
         <v>2027</v>
       </c>
       <c r="D1270">
-        <v>42.47351619067761</v>
+        <v>43.92044699251272</v>
       </c>
     </row>
     <row r="1271">
@@ -16883,7 +16883,7 @@
         <v>2028</v>
       </c>
       <c r="D1271">
-        <v>43.93727412322832</v>
+        <v>45.43377088784477</v>
       </c>
     </row>
     <row r="1272">
@@ -16922,7 +16922,7 @@
         <v>2026</v>
       </c>
       <c r="D1274">
-        <v>5.93880085668208</v>
+        <v>5.893855098017043</v>
       </c>
     </row>
     <row r="1275">
@@ -16935,7 +16935,7 @@
         <v>2027</v>
       </c>
       <c r="D1275">
-        <v>5.893968900693662</v>
+        <v>5.849315580691045</v>
       </c>
     </row>
     <row r="1276">
@@ -16948,7 +16948,7 @@
         <v>2028</v>
       </c>
       <c r="D1276">
-        <v>5.8494277634512</v>
+        <v>5.805112611645514</v>
       </c>
     </row>
     <row r="1277">
@@ -16987,7 +16987,7 @@
         <v>2026</v>
       </c>
       <c r="D1279">
-        <v>6.383997222240591</v>
+        <v>7.063132961622834</v>
       </c>
     </row>
     <row r="1280">
@@ -17000,7 +17000,7 @@
         <v>2027</v>
       </c>
       <c r="D1280">
-        <v>7.088986789917151</v>
+        <v>7.843076087668402</v>
       </c>
     </row>
     <row r="1281">
@@ -17013,7 +17013,7 @@
         <v>2028</v>
       </c>
       <c r="D1281">
-        <v>7.871784366283475</v>
+        <v>8.709144049559187</v>
       </c>
     </row>
     <row r="1282">
@@ -17052,7 +17052,7 @@
         <v>2026</v>
       </c>
       <c r="D1284">
-        <v>2.831333006798259</v>
+        <v>2.488107904048325</v>
       </c>
     </row>
     <row r="1285">
@@ -17065,7 +17065,7 @@
         <v>2027</v>
       </c>
       <c r="D1285">
-        <v>2.506771328349036</v>
+        <v>2.244762862535912</v>
       </c>
     </row>
     <row r="1286">
@@ -17078,7 +17078,7 @@
         <v>2028</v>
       </c>
       <c r="D1286">
-        <v>2.255252824432634</v>
+        <v>2.032887706713666</v>
       </c>
     </row>
     <row r="1287">
@@ -17117,7 +17117,7 @@
         <v>2026</v>
       </c>
       <c r="D1289">
-        <v>2.657860188299077</v>
+        <v>2.668463136821066</v>
       </c>
     </row>
     <row r="1290">
@@ -17130,7 +17130,7 @@
         <v>2027</v>
       </c>
       <c r="D1290">
-        <v>2.66808734053593</v>
+        <v>2.676508359556422</v>
       </c>
     </row>
     <row r="1291">
@@ -17143,7 +17143,7 @@
         <v>2028</v>
       </c>
       <c r="D1291">
-        <v>2.676413697841635</v>
+        <v>2.684269597147418</v>
       </c>
     </row>
     <row r="1292">
@@ -17182,7 +17182,7 @@
         <v>2026</v>
       </c>
       <c r="D1294">
-        <v>4.200591918670347</v>
+        <v>4.016132165822128</v>
       </c>
     </row>
     <row r="1295">
@@ -17195,7 +17195,7 @@
         <v>2027</v>
       </c>
       <c r="D1295">
-        <v>4.022369684679616</v>
+        <v>3.845945576399195</v>
       </c>
     </row>
     <row r="1296">
@@ -17208,7 +17208,7 @@
         <v>2028</v>
       </c>
       <c r="D1296">
-        <v>3.846629134737647</v>
+        <v>3.677809661991618</v>
       </c>
     </row>
     <row r="1297">
@@ -17247,7 +17247,7 @@
         <v>2026</v>
       </c>
       <c r="D1299">
-        <v>9.165181086420384</v>
+        <v>11.21475646963599</v>
       </c>
     </row>
     <row r="1300">
@@ -17260,7 +17260,7 @@
         <v>2027</v>
       </c>
       <c r="D1300">
-        <v>11.39236784652659</v>
+        <v>13.94007538302166</v>
       </c>
     </row>
     <row r="1301">
@@ -17273,7 +17273,7 @@
         <v>2028</v>
       </c>
       <c r="D1301">
-        <v>14.16084102259116</v>
+        <v>17.32769121511584</v>
       </c>
     </row>
     <row r="1302">
@@ -17312,7 +17312,7 @@
         <v>2026</v>
       </c>
       <c r="D1304">
-        <v>4.315103847301292</v>
+        <v>4.088421020912662</v>
       </c>
     </row>
     <row r="1305">
@@ -17325,7 +17325,7 @@
         <v>2027</v>
       </c>
       <c r="D1305">
-        <v>4.093192686951009</v>
+        <v>3.882496705156111</v>
       </c>
     </row>
     <row r="1306">
@@ -17338,7 +17338,7 @@
         <v>2028</v>
       </c>
       <c r="D1306">
-        <v>3.886418328341808</v>
+        <v>3.68833725895665</v>
       </c>
     </row>
     <row r="1307">
@@ -17377,7 +17377,7 @@
         <v>2026</v>
       </c>
       <c r="D1309">
-        <v>14.7895968549851</v>
+        <v>14.34180334000356</v>
       </c>
     </row>
     <row r="1310">
@@ -17390,7 +17390,7 @@
         <v>2027</v>
       </c>
       <c r="D1310">
-        <v>14.34620617574307</v>
+        <v>13.91188374311938</v>
       </c>
     </row>
     <row r="1311">
@@ -17403,7 +17403,7 @@
         <v>2028</v>
       </c>
       <c r="D1311">
-        <v>13.91618575212902</v>
+        <v>13.49487017326413</v>
       </c>
     </row>
     <row r="1312">
@@ -17442,7 +17442,7 @@
         <v>2026</v>
       </c>
       <c r="D1314">
-        <v>2.175532883388116</v>
+        <v>1.883586982766405</v>
       </c>
     </row>
     <row r="1315">
@@ -17455,7 +17455,7 @@
         <v>2027</v>
       </c>
       <c r="D1315">
-        <v>1.898154615194509</v>
+        <v>1.636614364868511</v>
       </c>
     </row>
     <row r="1316">
@@ -17468,7 +17468,7 @@
         <v>2028</v>
       </c>
       <c r="D1316">
-        <v>1.647156203143804</v>
+        <v>1.421267261796497</v>
       </c>
     </row>
     <row r="1317">
@@ -17507,7 +17507,7 @@
         <v>2026</v>
       </c>
       <c r="D1319">
-        <v>14.77870681136391</v>
+        <v>20.15108077692836</v>
       </c>
     </row>
     <row r="1320">
@@ -17520,7 +17520,7 @@
         <v>2027</v>
       </c>
       <c r="D1320">
-        <v>21.11521858304569</v>
+        <v>28.75396458838</v>
       </c>
     </row>
     <row r="1321">
@@ -17533,7 +17533,7 @@
         <v>2028</v>
       </c>
       <c r="D1321">
-        <v>29.8655354065267</v>
+        <v>40.69156085427176</v>
       </c>
     </row>
     <row r="1322">
@@ -17572,7 +17572,7 @@
         <v>2026</v>
       </c>
       <c r="D1324">
-        <v>5.025247180207713</v>
+        <v>4.375093004801221</v>
       </c>
     </row>
     <row r="1325">
@@ -17585,7 +17585,7 @@
         <v>2027</v>
       </c>
       <c r="D1325">
-        <v>4.597645719994698</v>
+        <v>4.1566914040504</v>
       </c>
     </row>
     <row r="1326">
@@ -17598,7 +17598,7 @@
         <v>2028</v>
       </c>
       <c r="D1326">
-        <v>4.014441918331719</v>
+        <v>3.511541346143535</v>
       </c>
     </row>
     <row r="1327">
@@ -17637,7 +17637,7 @@
         <v>2026</v>
       </c>
       <c r="D1329">
-        <v>14.21165625583852</v>
+        <v>12.95749360119563</v>
       </c>
     </row>
     <row r="1330">
@@ -17650,7 +17650,7 @@
         <v>2027</v>
       </c>
       <c r="D1330">
-        <v>12.94074905378514</v>
+        <v>11.79528208828236</v>
       </c>
     </row>
     <row r="1331">
@@ -17663,7 +17663,7 @@
         <v>2028</v>
       </c>
       <c r="D1331">
-        <v>11.85272225444782</v>
+        <v>10.80539107386546</v>
       </c>
     </row>
     <row r="1332">
@@ -17702,7 +17702,7 @@
         <v>2026</v>
       </c>
       <c r="D1334">
-        <v>12.73037379197154</v>
+        <v>11.8002191247142</v>
       </c>
     </row>
     <row r="1335">
@@ -17715,7 +17715,7 @@
         <v>2027</v>
       </c>
       <c r="D1335">
-        <v>11.82177264439668</v>
+        <v>10.95876765289155</v>
       </c>
     </row>
     <row r="1336">
@@ -17728,7 +17728,7 @@
         <v>2028</v>
       </c>
       <c r="D1336">
-        <v>10.9787687216968</v>
+        <v>10.17731938748467</v>
       </c>
     </row>
     <row r="1337">
@@ -17767,7 +17767,7 @@
         <v>2026</v>
       </c>
       <c r="D1339">
-        <v>45.64514806721744</v>
+        <v>46.56388950317361</v>
       </c>
     </row>
     <row r="1340">
@@ -17780,7 +17780,7 @@
         <v>2027</v>
       </c>
       <c r="D1340">
-        <v>46.57013689630961</v>
+        <v>47.50749642440505</v>
       </c>
     </row>
     <row r="1341">
@@ -17793,7 +17793,7 @@
         <v>2028</v>
       </c>
       <c r="D1341">
-        <v>47.51387041958537</v>
+        <v>48.47022533117746</v>
       </c>
     </row>
     <row r="1342">
@@ -17832,7 +17832,7 @@
         <v>2026</v>
       </c>
       <c r="D1344">
-        <v>44.96141116298514</v>
+        <v>49.1689182809754</v>
       </c>
     </row>
     <row r="1345">
@@ -17845,7 +17845,7 @@
         <v>2027</v>
       </c>
       <c r="D1345">
-        <v>47.06731211413558</v>
+        <v>49.62330460241516</v>
       </c>
     </row>
     <row r="1346">
@@ -17858,7 +17858,7 @@
         <v>2028</v>
       </c>
       <c r="D1346">
-        <v>51.63961624895018</v>
+        <v>56.12662586345998</v>
       </c>
     </row>
     <row r="1347">
@@ -17897,7 +17897,7 @@
         <v>2026</v>
       </c>
       <c r="D1349">
-        <v>31.02934966920662</v>
+        <v>29.93168276591691</v>
       </c>
     </row>
     <row r="1350">
@@ -17910,7 +17910,7 @@
         <v>2027</v>
       </c>
       <c r="D1350">
-        <v>29.94301601048386</v>
+        <v>28.88649976961814</v>
       </c>
     </row>
     <row r="1351">
@@ -17923,7 +17923,7 @@
         <v>2028</v>
       </c>
       <c r="D1351">
-        <v>28.89893887514955</v>
+        <v>27.87863408991362</v>
       </c>
     </row>
     <row r="1352">
@@ -17962,7 +17962,7 @@
         <v>2026</v>
       </c>
       <c r="D1354">
-        <v>10.39155375544135</v>
+        <v>9.052577430403058</v>
       </c>
     </row>
     <row r="1355">
@@ -17975,7 +17975,7 @@
         <v>2027</v>
       </c>
       <c r="D1355">
-        <v>9.107789371539869</v>
+        <v>7.949734163899675</v>
       </c>
     </row>
     <row r="1356">
@@ -17988,7 +17988,7 @@
         <v>2028</v>
       </c>
       <c r="D1356">
-        <v>7.995740178846678</v>
+        <v>6.984908942237305</v>
       </c>
     </row>
     <row r="1357">
@@ -18027,7 +18027,7 @@
         <v>2026</v>
       </c>
       <c r="D1359">
-        <v>20.86891892449902</v>
+        <v>22.03404551580298</v>
       </c>
     </row>
     <row r="1360">
@@ -18040,7 +18040,7 @@
         <v>2027</v>
       </c>
       <c r="D1360">
-        <v>22.0530674707409</v>
+        <v>23.28381195811727</v>
       </c>
     </row>
     <row r="1361">
@@ -18053,7 +18053,7 @@
         <v>2028</v>
       </c>
       <c r="D1361">
-        <v>23.30949700201248</v>
+        <v>24.61063353211719</v>
       </c>
     </row>
     <row r="1362">
@@ -18092,7 +18092,7 @@
         <v>2026</v>
       </c>
       <c r="D1364">
-        <v>45.49130543383546</v>
+        <v>55.54198883758524</v>
       </c>
     </row>
     <row r="1365">
@@ -18105,7 +18105,7 @@
         <v>2027</v>
       </c>
       <c r="D1365">
-        <v>55.78420559600671</v>
+        <v>68.04255852081462</v>
       </c>
     </row>
     <row r="1366">
@@ -18118,7 +18118,7 @@
         <v>2028</v>
       </c>
       <c r="D1366">
-        <v>69.44638300181403</v>
+        <v>84.75460164704222</v>
       </c>
     </row>
     <row r="1367">
@@ -18157,7 +18157,7 @@
         <v>2026</v>
       </c>
       <c r="D1369">
-        <v>23.17967922502746</v>
+        <v>22.59934538576445</v>
       </c>
     </row>
     <row r="1370">
@@ -18170,7 +18170,7 @@
         <v>2027</v>
       </c>
       <c r="D1370">
-        <v>22.61546115824001</v>
+        <v>22.10458888163953</v>
       </c>
     </row>
     <row r="1371">
@@ -18183,7 +18183,7 @@
         <v>2028</v>
       </c>
       <c r="D1371">
-        <v>22.11270902070912</v>
+        <v>21.63419279472337</v>
       </c>
     </row>
     <row r="1372">
@@ -18222,7 +18222,7 @@
         <v>2026</v>
       </c>
       <c r="D1374">
-        <v>24.602799876712</v>
+        <v>23.48294864287298</v>
       </c>
     </row>
     <row r="1375">
@@ -18235,7 +18235,7 @@
         <v>2027</v>
       </c>
       <c r="D1375">
-        <v>23.49943243455483</v>
+        <v>22.42981379534539</v>
       </c>
     </row>
     <row r="1376">
@@ -18248,7 +18248,7 @@
         <v>2028</v>
       </c>
       <c r="D1376">
-        <v>22.44555723372972</v>
+        <v>21.4239092629708</v>
       </c>
     </row>
     <row r="1377">
@@ -18287,7 +18287,7 @@
         <v>2026</v>
       </c>
       <c r="D1379">
-        <v>36.08950633517799</v>
+        <v>36.59903786187525</v>
       </c>
     </row>
     <row r="1380">
@@ -18300,7 +18300,7 @@
         <v>2027</v>
       </c>
       <c r="D1380">
-        <v>36.57585591723524</v>
+        <v>37.07601649501881</v>
       </c>
     </row>
     <row r="1381">
@@ -18313,7 +18313,7 @@
         <v>2028</v>
       </c>
       <c r="D1381">
-        <v>37.09714719732619</v>
+        <v>37.61638723508454</v>
       </c>
     </row>
     <row r="1382">
@@ -18352,7 +18352,7 @@
         <v>2026</v>
       </c>
       <c r="D1384">
-        <v>36.12574485715671</v>
+        <v>38.89790109739607</v>
       </c>
     </row>
     <row r="1385">
@@ -18365,7 +18365,7 @@
         <v>2027</v>
       </c>
       <c r="D1385">
-        <v>38.9783540634401</v>
+        <v>41.94635873988617</v>
       </c>
     </row>
     <row r="1386">
@@ -18378,7 +18378,7 @@
         <v>2028</v>
       </c>
       <c r="D1386">
-        <v>42.02444037136316</v>
+        <v>45.22906127680724</v>
       </c>
     </row>
   </sheetData>
